--- a/output/pdf_financials_xlsx/BRAG.xlsx
+++ b/output/pdf_financials_xlsx/BRAG.xlsx
@@ -865,31 +865,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.383722</v>
+        <v>0.796452</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.240215</v>
+        <v>0.555938</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.994513</v>
+        <v>2.794306</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.11616</v>
+        <v>3.029294</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.20201</v>
+        <v>5.010619</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.130779</v>
+        <v>4.895623</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>6.43443</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>3.913147</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.004962</v>
+        <v>11.367174</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0.014764</v>
@@ -917,28 +917,28 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.074188</v>
+        <v>-0.338542</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.093656</v>
+        <v>-0.222067</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.769984</v>
+        <v>-2.569777</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.157835</v>
+        <v>-2.755299</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.192425</v>
+        <v>-4.616184</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.728013</v>
+        <v>-3.036831</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1.334447</v>
+        <v>-5.099983</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.124675</v>
+        <v>-1.788472</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.004762</v>
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.173826</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.044008</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -2161,19 +2161,19 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.7965</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.181735</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.379996</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.9203519999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.266447</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.001859</v>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.173826</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.044008</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -2269,19 +2269,19 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.7965</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.181735</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.379996</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.9203519999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.266447</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.001859</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-0.075836</v>
+        <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.040665</v>
+        <v>0.116501</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>0.316331</v>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.175054</v>
+        <v>0.001228</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.04491</v>
+        <v>0.000902</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.343832</v>
+        <v>0.471496</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.638779</v>
+        <v>0.457044</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.391797</v>
+        <v>0.011801</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.237854</v>
+        <v>0.317502</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.330072</v>
+        <v>0.063625</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.000188</v>
@@ -18610,7 +18610,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -29322,7 +29322,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -56632,7 +56632,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E543" s="5" t="n">
@@ -60974,7 +60974,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -74768,7 +74768,7 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">

--- a/output/pdf_financials_xlsx/BRAG.xlsx
+++ b/output/pdf_financials_xlsx/BRAG.xlsx
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>4e-05</v>
+        <v>0.43077</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.00208</v>
@@ -1959,7 +1959,7 @@
         <v>-1.176934</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.004723</v>
+        <v>0.426007</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.007755</v>
@@ -2011,7 +2011,7 @@
         <v>-27.73109461498859</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-615.7757496740547</v>
+        <v>55541.98174706649</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>-29.16290613718411</v>
@@ -5791,7 +5791,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>4e-05</v>
+        <v>0.43077</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0.00208</v>
@@ -34521,7 +34521,11 @@
           <t>Additions of intangible assets 12</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -36756,7 +36760,11 @@
           <t>Additions of intangible assets 14</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -39972,7 +39980,11 @@
           <t>Additions of intangible assets 13</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -41693,7 +41705,11 @@
           <t>Additions in intangible assets 12</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -43238,7 +43254,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -44959,7 +44975,11 @@
           <t>Additions in intangible assets (Note 6)</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -56357,7 +56377,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">

--- a/output/pdf_financials_xlsx/BRAG.xlsx
+++ b/output/pdf_financials_xlsx/BRAG.xlsx
@@ -1469,10 +1469,10 @@
         <v>-1.176934</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0.013851</v>
+        <v>-0.004765</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-0.011947</v>
+        <v>-0.010376</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-0.007512</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>0.039866</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -3840,25 +3840,25 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.005399</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>5.146</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.001464</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.004327</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.007504</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.003236</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.009148</v>
       </c>
     </row>
     <row r="65">
@@ -4005,22 +4005,22 @@
         <v>1.610051</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>2.048</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.01238</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.014817</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.013983</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.016666</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.0163</v>
       </c>
     </row>
     <row r="68">
@@ -4056,25 +4056,25 @@
         <v>2.041335</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>1.610051</v>
+        <v>1.61545</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>7.194</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.013844</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>0.019144</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>0.021487</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>0.019902</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>0.025448</v>
       </c>
     </row>
     <row r="69">
@@ -4437,22 +4437,22 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.010121</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.01529</v>
+        <v>0.001446</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.023452</v>
+        <v>0.004308</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.027901</v>
+        <v>0.006414</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.022535</v>
+        <v>0.002633</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.029182</v>
+        <v>0.003734</v>
       </c>
     </row>
     <row r="76">
@@ -5733,10 +5733,10 @@
         <v>-1.788471</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-17.183838</v>
+        <v>-0.004765</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>-0.011947</v>
+        <v>-0.010376</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-0.007512</v>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003754</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -6426,10 +6426,10 @@
         </is>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009490999999999999</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.09481100000000001</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>-0.00012</v>
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003754</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -7792,10 +7792,10 @@
         </is>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009490999999999999</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.09481100000000001</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>-0.00012</v>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.213426</v>
+        <v>-0.21718</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.129818</v>
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-1.315356</v>
+        <v>-1.324847</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>0.000733</v>
+        <v>-0.09407799999999999</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-0.000218</v>
@@ -39264,7 +39264,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -39711,7 +39715,11 @@
           <t>Deferred income tax recovery 22</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -41430,7 +41438,11 @@
           <t>Deferred income tax recovery 8</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -44886,7 +44898,11 @@
           <t>Purchase of equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -48690,7 +48706,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E453" s="5" t="n">
         <v>-0.003754</v>
       </c>
@@ -51122,7 +51142,11 @@
           <t>Income taxes recovery (expense) 25</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -54522,7 +54546,11 @@
           <t>Net Loss From Continuing Operations</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -57089,7 +57117,11 @@
           <t>Net income from discontinued operations (Note 4)</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
